--- a/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0001T0006Z000C1N27_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0001T0006Z000C1N27_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>34.65245207174224</v>
+        <v>5.631023461658114</v>
       </c>
       <c r="D2" t="n">
-        <v>34.97289543221885</v>
+        <v>5.683095507735563</v>
       </c>
       <c r="E2" t="n">
-        <v>13.25356676014423</v>
+        <v>2.153704598523438</v>
       </c>
       <c r="F2" t="n">
-        <v>13.36953896832544</v>
+        <v>2.172550082352885</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>17.40343245604251</v>
+        <v>2.828057774106909</v>
       </c>
       <c r="D3" t="n">
-        <v>17.17317131490692</v>
+        <v>2.790640338672375</v>
       </c>
       <c r="E3" t="n">
-        <v>13.25356676014423</v>
+        <v>2.153704598523438</v>
       </c>
       <c r="F3" t="n">
-        <v>13.36953896832544</v>
+        <v>2.172550082352885</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>21.14241835530255</v>
+        <v>3.435642982736664</v>
       </c>
       <c r="D4" t="n">
-        <v>13.81798147864474</v>
+        <v>2.245421990279771</v>
       </c>
       <c r="E4" t="n">
-        <v>13.25356676014423</v>
+        <v>2.153704598523438</v>
       </c>
       <c r="F4" t="n">
-        <v>13.36953896832544</v>
+        <v>2.172550082352885</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>17.33463309379867</v>
+        <v>2.816877877742284</v>
       </c>
       <c r="D5" t="n">
-        <v>15.63693479111958</v>
+        <v>2.541001903556931</v>
       </c>
       <c r="E5" t="n">
-        <v>13.25356676014423</v>
+        <v>2.153704598523438</v>
       </c>
       <c r="F5" t="n">
-        <v>13.36953896832544</v>
+        <v>2.172550082352885</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>20.42669542166326</v>
+        <v>3.31933800602028</v>
       </c>
       <c r="D6" t="n">
-        <v>20.37924938209339</v>
+        <v>3.311628024590176</v>
       </c>
       <c r="E6" t="n">
-        <v>13.25356676014423</v>
+        <v>2.153704598523438</v>
       </c>
       <c r="F6" t="n">
-        <v>13.36953896832544</v>
+        <v>2.172550082352885</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>30.42490520850889</v>
+        <v>4.944047096382694</v>
       </c>
       <c r="D7" t="n">
-        <v>12.89628508378869</v>
+        <v>2.095646326115662</v>
       </c>
       <c r="E7" t="n">
-        <v>13.25356676014423</v>
+        <v>2.153704598523438</v>
       </c>
       <c r="F7" t="n">
-        <v>13.36953896832544</v>
+        <v>2.172550082352885</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>45.5864989629043</v>
+        <v>7.407806081471949</v>
       </c>
       <c r="D8" t="n">
-        <v>45.55915685588469</v>
+        <v>7.403362989081262</v>
       </c>
       <c r="E8" t="n">
-        <v>13.25356676014423</v>
+        <v>2.153704598523438</v>
       </c>
       <c r="F8" t="n">
-        <v>13.36953896832544</v>
+        <v>2.172550082352885</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>52.32940828457806</v>
+        <v>8.503528846243935</v>
       </c>
       <c r="D9" t="n">
-        <v>51.47108901038691</v>
+        <v>8.364051964187874</v>
       </c>
       <c r="E9" t="n">
-        <v>13.25356676014423</v>
+        <v>2.153704598523438</v>
       </c>
       <c r="F9" t="n">
-        <v>13.36953896832544</v>
+        <v>2.172550082352885</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>12.35693341443942</v>
+        <v>2.008001679846406</v>
       </c>
       <c r="D10" t="n">
-        <v>12.16353810018068</v>
+        <v>1.976574941279361</v>
       </c>
       <c r="E10" t="n">
-        <v>13.25356676014423</v>
+        <v>2.153704598523438</v>
       </c>
       <c r="F10" t="n">
-        <v>13.36953896832544</v>
+        <v>2.172550082352885</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>30.19688379270094</v>
+        <v>4.906993616313902</v>
       </c>
       <c r="D11" t="n">
-        <v>34.84678555101064</v>
+        <v>5.662602652039229</v>
       </c>
       <c r="E11" t="n">
-        <v>13.25356676014423</v>
+        <v>2.153704598523438</v>
       </c>
       <c r="F11" t="n">
-        <v>13.36953896832544</v>
+        <v>2.172550082352885</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>16.84405486371985</v>
+        <v>2.737158915354476</v>
       </c>
       <c r="D12" t="n">
-        <v>17.54915357147689</v>
+        <v>2.851737455364995</v>
       </c>
       <c r="E12" t="n">
-        <v>13.25356676014423</v>
+        <v>2.153704598523438</v>
       </c>
       <c r="F12" t="n">
-        <v>13.36953896832544</v>
+        <v>2.172550082352885</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>14.61538243357092</v>
+        <v>2.374999645455275</v>
       </c>
       <c r="D13" t="n">
-        <v>13.95745906478293</v>
+        <v>2.268087098027227</v>
       </c>
       <c r="E13" t="n">
-        <v>13.25356676014423</v>
+        <v>2.153704598523438</v>
       </c>
       <c r="F13" t="n">
-        <v>13.36953896832544</v>
+        <v>2.172550082352885</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>20.72416282162757</v>
+        <v>3.36767645851448</v>
       </c>
       <c r="D14" t="n">
-        <v>12.89570897807872</v>
+        <v>2.095552708937792</v>
       </c>
       <c r="E14" t="n">
-        <v>13.25356676014423</v>
+        <v>2.153704598523438</v>
       </c>
       <c r="F14" t="n">
-        <v>13.36953896832544</v>
+        <v>2.172550082352885</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>38.70097660864963</v>
+        <v>6.288908698905566</v>
       </c>
       <c r="D15" t="n">
-        <v>20.59591186541457</v>
+        <v>3.346835678129867</v>
       </c>
       <c r="E15" t="n">
-        <v>13.25356676014423</v>
+        <v>2.153704598523438</v>
       </c>
       <c r="F15" t="n">
-        <v>13.36953896832544</v>
+        <v>2.172550082352885</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>44.8206317077411</v>
+        <v>7.283352652507929</v>
       </c>
       <c r="D16" t="n">
-        <v>5.838790847378185</v>
+        <v>0.948803512698955</v>
       </c>
       <c r="E16" t="n">
-        <v>13.25356676014423</v>
+        <v>2.153704598523438</v>
       </c>
       <c r="F16" t="n">
-        <v>13.36953896832544</v>
+        <v>2.172550082352885</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>41.84553126351777</v>
+        <v>6.799898830321638</v>
       </c>
       <c r="D17" t="n">
-        <v>11.23610252712212</v>
+        <v>1.825866660657344</v>
       </c>
       <c r="E17" t="n">
-        <v>13.25356676014423</v>
+        <v>2.153704598523438</v>
       </c>
       <c r="F17" t="n">
-        <v>13.36953896832544</v>
+        <v>2.172550082352885</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>9.933413844206457</v>
+        <v>1.614179749683549</v>
       </c>
       <c r="D18" t="n">
-        <v>8.690611920198204</v>
+        <v>1.412224437032208</v>
       </c>
       <c r="E18" t="n">
-        <v>13.25356676014423</v>
+        <v>2.153704598523438</v>
       </c>
       <c r="F18" t="n">
-        <v>13.36953896832544</v>
+        <v>2.172550082352885</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>23.90455558628476</v>
+        <v>3.884490282771274</v>
       </c>
       <c r="D19" t="n">
-        <v>29.56926243331442</v>
+        <v>4.805005145413594</v>
       </c>
       <c r="E19" t="n">
-        <v>13.25356676014423</v>
+        <v>2.153704598523438</v>
       </c>
       <c r="F19" t="n">
-        <v>13.36953896832544</v>
+        <v>2.172550082352885</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>7.723314651947651</v>
+        <v>1.255038630941493</v>
       </c>
       <c r="D20" t="n">
-        <v>6.894896466505173</v>
+        <v>1.120420675807091</v>
       </c>
       <c r="E20" t="n">
-        <v>13.25356676014423</v>
+        <v>2.153704598523438</v>
       </c>
       <c r="F20" t="n">
-        <v>13.36953896832544</v>
+        <v>2.172550082352885</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>7.657333685732534</v>
+        <v>1.244316723931537</v>
       </c>
       <c r="D21" t="n">
-        <v>44.37151586410875</v>
+        <v>7.210371327917672</v>
       </c>
       <c r="E21" t="n">
-        <v>13.25356676014423</v>
+        <v>2.153704598523438</v>
       </c>
       <c r="F21" t="n">
-        <v>13.36953896832544</v>
+        <v>2.172550082352885</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
